--- a/datasets/100_samples_shirazi.xlsx
+++ b/datasets/100_samples_shirazi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Personal Projects\SilkRoadNLP\Repositories\General\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0B76B3-8331-4CD1-92EA-DC4509F07812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA537B3C-BD87-4126-A5F3-0A8D5D9C0D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="334">
   <si>
     <t>100_samples</t>
   </si>
@@ -1047,9 +1047,6 @@
     <t>ما عَم میویم.</t>
   </si>
   <si>
-    <t>دس بجنبون</t>
-  </si>
-  <si>
     <t>پس کجویی عزیزُم؟</t>
   </si>
   <si>
@@ -1071,9 +1068,6 @@
     <t>قدوی سرت. عیبی نداره.</t>
   </si>
   <si>
-    <t>آفتاب از کدوم سمت درومده؟ / امروز کُجُ دس و رومه شسّه بودم؟</t>
-  </si>
-  <si>
     <t>خانوم بچه‌ها چیطورن؟</t>
   </si>
   <si>
@@ -1108,6 +1102,129 @@
   </si>
   <si>
     <t>گربُو ره بُراق کِرده.</t>
+  </si>
+  <si>
+    <t>امروز کُجُ دس و رومه شسّه بودم؟</t>
+  </si>
+  <si>
+    <t>اَی امر حضرت حق نباشه، برگ از درخت نَمیوفته.</t>
+  </si>
+  <si>
+    <t>اَی نخوردیم نونِ گندم، ولی دیدیم دسِّ مردم.</t>
+  </si>
+  <si>
+    <t>جار</t>
+  </si>
+  <si>
+    <t>خسّه</t>
+  </si>
+  <si>
+    <t>بوگو چقدر حال می‌ده</t>
+  </si>
+  <si>
+    <t>لعنت به پدرت</t>
+  </si>
+  <si>
+    <t>هکروی ما از هکروی دیگه چیزی کم ندارن</t>
+  </si>
+  <si>
+    <t>خیلی جالب می‌شه</t>
+  </si>
+  <si>
+    <t>فقط وُیسو برِی یکی از بازیوی باحالت</t>
+  </si>
+  <si>
+    <t>ما برِی تازه‌ترین آتیش منتظر می‌مونیم</t>
+  </si>
+  <si>
+    <t>یعنی ساخته نمی‌شه</t>
+  </si>
+  <si>
+    <t>با ایکه ده تو کارگر داره،‌ پونزده سال طول می‌کشه</t>
+  </si>
+  <si>
+    <t>مِثکه کسوی دیگه‌ای هم با هواپیما به لوگر می‌رن</t>
+  </si>
+  <si>
+    <t>ساختن ای فرودگاهو هم عین رفتن به ماعه</t>
+  </si>
+  <si>
+    <t>درخت میوه کرم از خودشه</t>
+  </si>
+  <si>
+    <t>بیرون باغُ که دیدیم، انگو تا تَهِ باغُ دیدیم.</t>
+  </si>
+  <si>
+    <t>حرفه اَی داخل شیشه کنی به بیرون درز می‌کنه.</t>
+  </si>
+  <si>
+    <t>حرف تا وقتی تو دلته اختیارش دسِّته.</t>
+  </si>
+  <si>
+    <t>دل که سفره نیست که پیش همه پهنش کنی.</t>
+  </si>
+  <si>
+    <t>خرسو به آهنگری بسَّن.</t>
+  </si>
+  <si>
+    <t>ای آبُ تو هوَنگ کنه که بوکوبی، نَمی‌ذاره بیکار باشی.</t>
+  </si>
+  <si>
+    <t>کور اَی بازار نره بازار می‌گنده.</t>
+  </si>
+  <si>
+    <t>آیت کارت آخره.</t>
+  </si>
+  <si>
+    <t>چاکَن همیشه تهِ چاهه.</t>
+  </si>
+  <si>
+    <t>قیمت غذا نسبت به حجم غذا خیلی خیلی گرون و غیرمنصفانه‌ن. ساندویچ هیولُی ژامبون در حد یِی بچه غولی هم نبود و اصلاً هم خوشمزه نبود اما ساندویچ چوریتسو عالی و بسیار بسیار خوشمزه بود.</t>
+  </si>
+  <si>
+    <t>لطف کنید از عکسوی اینترنتی استفاده نکنید و عکس خود محصولتونه بذارین. آخه ای کجو و او کجو. متأسفم.</t>
+  </si>
+  <si>
+    <t>حجم ساندویچش کلاً نصف شده!</t>
+  </si>
+  <si>
+    <t>فوق‌العاده بی‌نمک بود و بوی تند گوشت می‌داد.</t>
+  </si>
+  <si>
+    <t>اول ایکه بوی بدی دُشت دوم ایکه به همه چی می‌خورد به جز رست بیف جوری که منو یاد گوشت آبپز داخل آبگوشت انداخت خیلی خیس بود نون خشک و بدمزه‌ای دُشت لطفاً تناسب مایعاته رعایت کنین احتمالاً آخرین باره که از اینجو سفارش می‌دم.</t>
+  </si>
+  <si>
+    <t>خو پَ چرو نمیوی؟</t>
+  </si>
+  <si>
+    <t>چاقوی تیز برِی بره نر اومده.</t>
+  </si>
+  <si>
+    <t>برِی خودت بخور، برِی مردم بوپوش.</t>
+  </si>
+  <si>
+    <t>سفره بابوی شُمو سر کوچه‌ن.</t>
+  </si>
+  <si>
+    <t>خدا خره دید بهش شاخ نداد</t>
+  </si>
+  <si>
+    <t>طرف ماره کشته، بچِی ماره زنده گُذُشته.</t>
+  </si>
+  <si>
+    <t>گند بخوره به کارت.</t>
+  </si>
+  <si>
+    <t>چشم زمسّون کوره.</t>
+  </si>
+  <si>
+    <t>انگُ اوره خانُم زُیده ما رِ کنیز.</t>
+  </si>
+  <si>
+    <t>می‌خواما یخه‌مه پاره کنم</t>
+  </si>
+  <si>
+    <t>زودی باش / دس بجنبون</t>
   </si>
 </sst>
 </file>
@@ -1316,11 +1433,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2467,15 +2584,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.6" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:10" ht="20.25" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -2532,10 +2649,6 @@
       <c r="H3" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="I3" s="1">
-        <f>COUNTBLANK(H3:H102)</f>
-        <v>42</v>
-      </c>
     </row>
     <row r="4" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="6" t="s">
@@ -2663,8 +2776,8 @@
       <c r="G8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="12" t="s">
-        <v>282</v>
+      <c r="H8" s="11" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="20.100000000000001" customHeight="1">
@@ -2872,7 +2985,7 @@
         <v>48</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -2924,7 +3037,7 @@
         <v>41</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -3002,7 +3115,7 @@
         <v>41</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -3028,7 +3141,7 @@
         <v>41</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -3131,6 +3244,9 @@
       <c r="G26" s="8" t="s">
         <v>74</v>
       </c>
+      <c r="H26" s="1" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A27" s="6" t="s">
@@ -3154,6 +3270,9 @@
       <c r="G27" s="8" t="s">
         <v>74</v>
       </c>
+      <c r="H27" s="1" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="6" t="s">
@@ -3178,7 +3297,7 @@
         <v>79</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -3229,6 +3348,9 @@
       <c r="G30" s="8" t="s">
         <v>66</v>
       </c>
+      <c r="H30" s="1" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A31" s="6" t="s">
@@ -3252,6 +3374,9 @@
       <c r="G31" s="8" t="s">
         <v>66</v>
       </c>
+      <c r="H31" s="1" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="6" t="s">
@@ -3275,8 +3400,11 @@
       <c r="G32" s="8" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="H32" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A33" s="6" t="s">
         <v>89</v>
       </c>
@@ -3298,8 +3426,11 @@
       <c r="G33" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="H33" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A34" s="6" t="s">
         <v>89</v>
       </c>
@@ -3321,8 +3452,11 @@
       <c r="G34" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="H34" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A35" s="6" t="s">
         <v>89</v>
       </c>
@@ -3344,8 +3478,11 @@
       <c r="G35" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="H35" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A36" s="6" t="s">
         <v>89</v>
       </c>
@@ -3367,8 +3504,11 @@
       <c r="G36" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="H36" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A37" s="6" t="s">
         <v>89</v>
       </c>
@@ -3390,8 +3530,11 @@
       <c r="G37" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="H37" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A38" s="6" t="s">
         <v>89</v>
       </c>
@@ -3413,8 +3556,11 @@
       <c r="G38" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="H38" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A39" s="6" t="s">
         <v>89</v>
       </c>
@@ -3436,8 +3582,11 @@
       <c r="G39" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="H39" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A40" s="6" t="s">
         <v>89</v>
       </c>
@@ -3459,8 +3608,11 @@
       <c r="G40" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="H40" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A41" s="6" t="s">
         <v>89</v>
       </c>
@@ -3482,8 +3634,11 @@
       <c r="G41" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="H41" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A42" s="6" t="s">
         <v>89</v>
       </c>
@@ -3505,8 +3660,11 @@
       <c r="G42" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="35.549999999999997" customHeight="1">
+      <c r="H42" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="35.549999999999997" customHeight="1">
       <c r="A43" s="6" t="s">
         <v>113</v>
       </c>
@@ -3528,8 +3686,11 @@
       <c r="G43" s="8" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="35.549999999999997" customHeight="1">
+      <c r="H43" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="35.549999999999997" customHeight="1">
       <c r="A44" s="6" t="s">
         <v>113</v>
       </c>
@@ -3551,8 +3712,11 @@
       <c r="G44" s="8" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="35.549999999999997" customHeight="1">
+      <c r="H44" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="35.549999999999997" customHeight="1">
       <c r="A45" s="6" t="s">
         <v>113</v>
       </c>
@@ -3574,8 +3738,11 @@
       <c r="G45" s="8" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="35.549999999999997" customHeight="1">
+      <c r="H45" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="35.549999999999997" customHeight="1">
       <c r="A46" s="6" t="s">
         <v>113</v>
       </c>
@@ -3597,8 +3764,11 @@
       <c r="G46" s="8" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="35.549999999999997" customHeight="1">
+      <c r="H46" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="35.549999999999997" customHeight="1">
       <c r="A47" s="6" t="s">
         <v>113</v>
       </c>
@@ -3620,8 +3790,11 @@
       <c r="G47" s="8" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="35.549999999999997" customHeight="1">
+      <c r="H47" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="35.549999999999997" customHeight="1">
       <c r="A48" s="6" t="s">
         <v>113</v>
       </c>
@@ -3642,6 +3815,9 @@
       </c>
       <c r="G48" s="8" t="s">
         <v>118</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="35.549999999999997" customHeight="1">
@@ -3666,6 +3842,9 @@
       <c r="G49" s="8" t="s">
         <v>118</v>
       </c>
+      <c r="H49" s="1" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="50" spans="1:8" ht="35.549999999999997" customHeight="1">
       <c r="A50" s="6" t="s">
@@ -3689,6 +3868,9 @@
       <c r="G50" s="8" t="s">
         <v>118</v>
       </c>
+      <c r="H50" s="1" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="51" spans="1:8" ht="35.549999999999997" customHeight="1">
       <c r="A51" s="6" t="s">
@@ -3712,6 +3894,9 @@
       <c r="G51" s="8" t="s">
         <v>118</v>
       </c>
+      <c r="H51" s="1" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="52" spans="1:8" ht="35.549999999999997" customHeight="1">
       <c r="A52" s="6" t="s">
@@ -3735,6 +3920,9 @@
       <c r="G52" s="8" t="s">
         <v>118</v>
       </c>
+      <c r="H52" s="1" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A53" s="6" t="s">
@@ -3758,6 +3946,9 @@
       <c r="G53" s="8" t="s">
         <v>139</v>
       </c>
+      <c r="H53" s="1" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A54" s="6" t="s">
@@ -3781,6 +3972,9 @@
       <c r="G54" s="8" t="s">
         <v>139</v>
       </c>
+      <c r="H54" s="1" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A55" s="6" t="s">
@@ -3908,6 +4102,9 @@
       <c r="G59" s="8" t="s">
         <v>139</v>
       </c>
+      <c r="H59" s="1" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A60" s="6" t="s">
@@ -3957,6 +4154,9 @@
       <c r="G61" s="8" t="s">
         <v>139</v>
       </c>
+      <c r="H61" s="1" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A62" s="6" t="s">
@@ -3980,6 +4180,9 @@
       <c r="G62" s="8" t="s">
         <v>139</v>
       </c>
+      <c r="H62" s="1" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A63" s="6" t="s">
@@ -4033,7 +4236,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="65" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A65" s="6" t="s">
         <v>113</v>
       </c>
@@ -4055,11 +4258,11 @@
       <c r="G65" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="I65" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="20.100000000000001" customHeight="1">
+      <c r="H65" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A66" s="6" t="s">
         <v>113</v>
       </c>
@@ -4082,10 +4285,10 @@
         <v>159</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="20.100000000000001" customHeight="1">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A67" s="6" t="s">
         <v>113</v>
       </c>
@@ -4108,10 +4311,10 @@
         <v>159</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="20.100000000000001" customHeight="1">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A68" s="6" t="s">
         <v>113</v>
       </c>
@@ -4137,7 +4340,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="69" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A69" s="6" t="s">
         <v>113</v>
       </c>
@@ -4163,7 +4366,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="70" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A70" s="6" t="s">
         <v>113</v>
       </c>
@@ -4186,10 +4389,10 @@
         <v>152</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="20.100000000000001" customHeight="1">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A71" s="6" t="s">
         <v>113</v>
       </c>
@@ -4211,8 +4414,11 @@
       <c r="G71" s="8" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" ht="20.100000000000001" customHeight="1">
+      <c r="H71" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A72" s="6" t="s">
         <v>113</v>
       </c>
@@ -4235,10 +4441,10 @@
         <v>159</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="20.100000000000001" customHeight="1">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A73" s="6" t="s">
         <v>113</v>
       </c>
@@ -4260,11 +4466,11 @@
       <c r="G73" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H73" s="8" t="s">
+      <c r="H73" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="74" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A74" s="6" t="s">
         <v>113</v>
       </c>
@@ -4286,11 +4492,11 @@
       <c r="G74" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H74" s="8" t="s">
+      <c r="H74" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="75" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A75" s="6" t="s">
         <v>113</v>
       </c>
@@ -4312,11 +4518,11 @@
       <c r="G75" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H75" s="8" t="s">
+      <c r="H75" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="76" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A76" s="6" t="s">
         <v>113</v>
       </c>
@@ -4338,11 +4544,11 @@
       <c r="G76" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="H76" s="8" t="s">
+      <c r="H76" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="77" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A77" s="6" t="s">
         <v>113</v>
       </c>
@@ -4364,11 +4570,11 @@
       <c r="G77" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="H77" s="8" t="s">
+      <c r="H77" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="78" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A78" s="6" t="s">
         <v>113</v>
       </c>
@@ -4390,11 +4596,11 @@
       <c r="G78" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="H78" s="8" t="s">
+      <c r="H78" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="79" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A79" s="6" t="s">
         <v>113</v>
       </c>
@@ -4416,11 +4622,11 @@
       <c r="G79" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H79" s="8" t="s">
+      <c r="H79" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="80" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A80" s="6" t="s">
         <v>113</v>
       </c>
@@ -4442,7 +4648,7 @@
       <c r="G80" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H80" s="8" t="s">
+      <c r="H80" s="1" t="s">
         <v>190</v>
       </c>
     </row>
@@ -4468,7 +4674,7 @@
       <c r="G81" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H81" s="8" t="s">
+      <c r="H81" s="1" t="s">
         <v>192</v>
       </c>
     </row>
@@ -4494,7 +4700,7 @@
       <c r="G82" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H82" s="8" t="s">
+      <c r="H82" s="1" t="s">
         <v>194</v>
       </c>
     </row>
@@ -4520,6 +4726,9 @@
       <c r="G83" s="8" t="s">
         <v>199</v>
       </c>
+      <c r="H83" s="1" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="84" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A84" s="6" t="s">
@@ -4543,6 +4752,9 @@
       <c r="G84" s="8" t="s">
         <v>199</v>
       </c>
+      <c r="H84" s="1" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="85" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A85" s="6" t="s">
@@ -4566,6 +4778,9 @@
       <c r="G85" s="8" t="s">
         <v>204</v>
       </c>
+      <c r="H85" s="1" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="86" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A86" s="6" t="s">
@@ -4590,7 +4805,7 @@
         <v>207</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -4616,7 +4831,7 @@
         <v>207</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -4641,6 +4856,9 @@
       <c r="G88" s="8" t="s">
         <v>212</v>
       </c>
+      <c r="H88" s="1" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="89" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A89" s="6" t="s">
@@ -4664,6 +4882,9 @@
       <c r="G89" s="8" t="s">
         <v>204</v>
       </c>
+      <c r="H89" s="1" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="90" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A90" s="6" t="s">
@@ -4687,6 +4908,9 @@
       <c r="G90" s="8" t="s">
         <v>199</v>
       </c>
+      <c r="H90" s="1" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="91" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A91" s="6" t="s">
@@ -4710,6 +4934,9 @@
       <c r="G91" s="8" t="s">
         <v>199</v>
       </c>
+      <c r="H91" s="1" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="92" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A92" s="6" t="s">
@@ -4734,7 +4961,7 @@
         <v>199</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -4760,7 +4987,7 @@
         <v>41</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -4786,7 +5013,7 @@
         <v>41</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -4811,6 +5038,9 @@
       <c r="G95" s="8" t="s">
         <v>41</v>
       </c>
+      <c r="H95" s="11" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="96" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A96" s="6" t="s">
@@ -4835,7 +5065,7 @@
         <v>41</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -4861,7 +5091,7 @@
         <v>233</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -4887,7 +5117,7 @@
         <v>236</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -4913,7 +5143,7 @@
         <v>239</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -4938,6 +5168,9 @@
       <c r="G100" s="8" t="s">
         <v>242</v>
       </c>
+      <c r="H100" s="1" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="101" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A101" s="6" t="s">
@@ -4961,6 +5194,9 @@
       <c r="G101" s="8" t="s">
         <v>41</v>
       </c>
+      <c r="H101" s="1" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="102" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A102" s="6" t="s">
@@ -4985,7 +5221,7 @@
         <v>41</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/100_samples_shirazi.xlsx
+++ b/datasets/100_samples_shirazi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Personal Projects\SilkRoadNLP\Repositories\General\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA537B3C-BD87-4126-A5F3-0A8D5D9C0D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADD8B71-80E9-483E-BACC-E5F73E4ACA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="435">
   <si>
     <t>100_samples</t>
   </si>
@@ -978,9 +978,6 @@
     <t>خرس بخورتش می‌پوکه.</t>
   </si>
   <si>
-    <t>من چوی نَمی‌خورم</t>
-  </si>
-  <si>
     <t>عالی بود؛ بوس به جونت، قربونت برم</t>
   </si>
   <si>
@@ -1005,9 +1002,6 @@
     <t>تو کل عمرُم همچی غذاهوی نخوردم</t>
   </si>
   <si>
-    <t>دسِّتون درد نکنه بری پخش ای کلیپ درباره گیوه هرسینی</t>
-  </si>
-  <si>
     <t>بیشترشونو اولین باره می‌بینم</t>
   </si>
   <si>
@@ -1032,54 +1026,27 @@
     <t>جوی کیک وانیلی کاکائویی، کیک کاکايویی ساده ارسال شده بود.</t>
   </si>
   <si>
-    <t>خورشش مزِی آب می‌داد و ۹۵ درصد حجم قیمه‌ش لپه بود. اصلا پیشنهاد نَمی‌کنم.</t>
-  </si>
-  <si>
     <t>خیلی عالی و به‌موقع. ممنون از شُمو.</t>
   </si>
   <si>
-    <t>عالی. فقط جوی یِی چنگالی خالی بود</t>
-  </si>
-  <si>
     <t>پس چرو نَمیوی؟</t>
   </si>
   <si>
     <t>ما عَم میویم.</t>
   </si>
   <si>
-    <t>پس کجویی عزیزُم؟</t>
-  </si>
-  <si>
-    <t>بیو بریم ناهار بخوریم. وُی نه، یِی چی آشغالی خوردم، دلُم ریخته به هم.</t>
-  </si>
-  <si>
     <t>پنج و چار و سه</t>
   </si>
   <si>
     <t>کَمَرُم پُکید.</t>
   </si>
   <si>
-    <t>ای شکوفه‌ها چه قشنگن.</t>
-  </si>
-  <si>
     <t>خونِی شومو.</t>
   </si>
   <si>
-    <t>قدوی سرت. عیبی نداره.</t>
-  </si>
-  <si>
-    <t>خانوم بچه‌ها چیطورن؟</t>
-  </si>
-  <si>
-    <t>ای داد و بیداد برای میراث پدرامون که بی پشت و پنا موندن</t>
-  </si>
-  <si>
     <t>درود فراوون به زنوی کورد سر تا سر دنیا از کرمونشا گرفته تا کردستان</t>
   </si>
   <si>
-    <t>هر وقت نون درست می‌کِرد صدامون می‌زد. ما بچّا هم همگی به‌صف کنارش می‌شنسّیم و چشم به را می‌موندیم تا نون روی تووه برشته می‌شد و می‌داد دسّمون.</t>
-  </si>
-  <si>
     <t>او چیچیه که تا دس تو چیشش نکنی، چیلشه باز نَمی‌کنه؟</t>
   </si>
   <si>
@@ -1095,12 +1062,6 @@
     <t>عبده ای کی بود؟</t>
   </si>
   <si>
-    <t>تور خدا بفرمو داخل خونه.</t>
-  </si>
-  <si>
-    <t>دماغش چقد پهنه. لباش شبیه پشت میمونه.</t>
-  </si>
-  <si>
     <t>گربُو ره بُراق کِرده.</t>
   </si>
   <si>
@@ -1119,9 +1080,6 @@
     <t>خسّه</t>
   </si>
   <si>
-    <t>بوگو چقدر حال می‌ده</t>
-  </si>
-  <si>
     <t>لعنت به پدرت</t>
   </si>
   <si>
@@ -1137,18 +1095,9 @@
     <t>ما برِی تازه‌ترین آتیش منتظر می‌مونیم</t>
   </si>
   <si>
-    <t>یعنی ساخته نمی‌شه</t>
-  </si>
-  <si>
-    <t>با ایکه ده تو کارگر داره،‌ پونزده سال طول می‌کشه</t>
-  </si>
-  <si>
     <t>مِثکه کسوی دیگه‌ای هم با هواپیما به لوگر می‌رن</t>
   </si>
   <si>
-    <t>ساختن ای فرودگاهو هم عین رفتن به ماعه</t>
-  </si>
-  <si>
     <t>درخت میوه کرم از خودشه</t>
   </si>
   <si>
@@ -1161,9 +1110,6 @@
     <t>حرف تا وقتی تو دلته اختیارش دسِّته.</t>
   </si>
   <si>
-    <t>دل که سفره نیست که پیش همه پهنش کنی.</t>
-  </si>
-  <si>
     <t>خرسو به آهنگری بسَّن.</t>
   </si>
   <si>
@@ -1176,9 +1122,6 @@
     <t>آیت کارت آخره.</t>
   </si>
   <si>
-    <t>چاکَن همیشه تهِ چاهه.</t>
-  </si>
-  <si>
     <t>قیمت غذا نسبت به حجم غذا خیلی خیلی گرون و غیرمنصفانه‌ن. ساندویچ هیولُی ژامبون در حد یِی بچه غولی هم نبود و اصلاً هم خوشمزه نبود اما ساندویچ چوریتسو عالی و بسیار بسیار خوشمزه بود.</t>
   </si>
   <si>
@@ -1197,15 +1140,9 @@
     <t>خو پَ چرو نمیوی؟</t>
   </si>
   <si>
-    <t>چاقوی تیز برِی بره نر اومده.</t>
-  </si>
-  <si>
     <t>برِی خودت بخور، برِی مردم بوپوش.</t>
   </si>
   <si>
-    <t>سفره بابوی شُمو سر کوچه‌ن.</t>
-  </si>
-  <si>
     <t>خدا خره دید بهش شاخ نداد</t>
   </si>
   <si>
@@ -1224,14 +1161,390 @@
     <t>می‌خواما یخه‌مه پاره کنم</t>
   </si>
   <si>
-    <t>زودی باش / دس بجنبون</t>
+    <t>Dāram miram</t>
+  </si>
+  <si>
+    <t>Man choy namkhoram</t>
+  </si>
+  <si>
+    <t>من چوی نَمخورم</t>
+  </si>
+  <si>
+    <t>Āli bud; bus be junet, qorbunet beram</t>
+  </si>
+  <si>
+    <t>Emruz kojo daso rume shosse budam?</t>
+  </si>
+  <si>
+    <t>Ire khodā zadeh</t>
+  </si>
+  <si>
+    <t>Chi doros kerdi?</t>
+  </si>
+  <si>
+    <t>Dokhtarā dāran miran</t>
+  </si>
+  <si>
+    <t>Dokhtarā doshtan miraftan</t>
+  </si>
+  <si>
+    <t>Ravānshenāsā khavāse ziādi barey gerye kerdan dar ovordan va gerye kerdane barey rahā shodan az feshāre esteres va tahammole dardo ghamo ghose midunan.</t>
+  </si>
+  <si>
+    <t>U morabow khordan dāreh</t>
+  </si>
+  <si>
+    <t>خانوم بچّا چیطورن؟</t>
+  </si>
+  <si>
+    <t>Khanum bachchā chitoran?</t>
+  </si>
+  <si>
+    <t>دسِّتون درد نکنه بری پخش ای کیلیپ دربارِی گیوِی هرسینی</t>
+  </si>
+  <si>
+    <t>Dassetun dard nakoneh barey pakhshe i kilip darbārey givey harsini</t>
+  </si>
+  <si>
+    <t>Ey dādo bidād barey mirāse pedarāmun ke bi poshto pana mondan</t>
+  </si>
+  <si>
+    <t>ای داد و بیداد بری میراث پدرامون که بی پشت و پنا مُندن</t>
+  </si>
+  <si>
+    <t>Bishtareshuno avalin bāre mibinam</t>
+  </si>
+  <si>
+    <t>Ey junom barey shahremun</t>
+  </si>
+  <si>
+    <t>Dorude farāvun be zanoy korde sar tā sare donyā az kermunshā gerefte ta kordestān</t>
+  </si>
+  <si>
+    <t>Har vaght nun doros mikerd sedāmun mizad. Mā bachchā ham hamegi be saf kenāresh mishnessimo cheshm be rā mimondim tā nun ruye towe bereshte mishodo midād dassemun.</t>
+  </si>
+  <si>
+    <t>هر وقت نون دُرُس می‌کِرد صدامون می‌زد. ما بچّا هم همگی به‌صف کنارش می‌شنسّیم و چشم به را می‌مُندیم تا نون روی توه برشته می‌شد و می‌داد دسّمون.</t>
+  </si>
+  <si>
+    <t>Bordano ovordan</t>
+  </si>
+  <si>
+    <t>Dādo bidād</t>
+  </si>
+  <si>
+    <t>Khodā negadār</t>
+  </si>
+  <si>
+    <t>Ay amre hazrate haq nabāshe, barg az derakht namiofteh.</t>
+  </si>
+  <si>
+    <t>Ay nakhordim nune gandom, vali didim dasse mardom.</t>
+  </si>
+  <si>
+    <t>U chichieh keh tā das to chishesh nakoni, chileshe bāz namikoneh?</t>
+  </si>
+  <si>
+    <t>Mey behet zang nazadan?</t>
+  </si>
+  <si>
+    <t>Jār</t>
+  </si>
+  <si>
+    <t>Khasse</t>
+  </si>
+  <si>
+    <t>Farār</t>
+  </si>
+  <si>
+    <t>Tu kolle omrom hamchi ghazāhoy nakhordam</t>
+  </si>
+  <si>
+    <t>Bugu cheqad hāl mideh</t>
+  </si>
+  <si>
+    <t>بوگو چقد حال می‌ده</t>
+  </si>
+  <si>
+    <t>La‘nat be pedaret</t>
+  </si>
+  <si>
+    <t>Hakeroy mā az hakeroy digeh chizi kam nadāran</t>
+  </si>
+  <si>
+    <t>Kheili jāleb misheh</t>
+  </si>
+  <si>
+    <t>Faghat voyso barey yeki az bāzioy bāhālet</t>
+  </si>
+  <si>
+    <t>Ma barey tāzetarin ātish montazer mimunim</t>
+  </si>
+  <si>
+    <t>یَنی ساخته نمی‌شه</t>
+  </si>
+  <si>
+    <t>Yani sakhteh namisheh</t>
+  </si>
+  <si>
+    <t>با ایکه دَ تو کارگر داره،‌ پونزَ سال طول می‌کشه</t>
+  </si>
+  <si>
+    <t>Bā ike da to kārgar dāreh, punza sāl tul mikeshe</t>
+  </si>
+  <si>
+    <t>Meske kasoy degei ham bā hāvāpeyma be logar miran</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Derakhte mive kerm az khodeshe</t>
+  </si>
+  <si>
+    <t>Birune bāgho ke didim, engo tā tahe bāgho didim.</t>
+  </si>
+  <si>
+    <t>Hareh ay dākhele shisheh koni beh birun darz mikoneh.</t>
+  </si>
+  <si>
+    <t>دل که سفره نیس که پیش همه پهنش کنی.</t>
+  </si>
+  <si>
+    <t>Del ke sofre nis ke pishe hame pahnesh koni.</t>
+  </si>
+  <si>
+    <t>Kherso be āhangari bassan.</t>
+  </si>
+  <si>
+    <t>Ay ābo tu howang koneh ke bukubi, namizāreh bikār bāshi.</t>
+  </si>
+  <si>
+    <t>Kur ay bāzār nareh bāzār migandeh.</t>
+  </si>
+  <si>
+    <t>Āyat kāret akhere.</t>
+  </si>
+  <si>
+    <t>Chākan hamisheh ta chāheh.</t>
+  </si>
+  <si>
+    <t>چاکَن همیشه تَ چاهه.</t>
+  </si>
+  <si>
+    <t>Qeymate ghazā nesbat beh hajme ghazā kheili geruno gheyremonsefānan. Sāndeviche hayuloy zhāmbon dar hadde yey bachche ghuli ham nabud va aslan ham khoshmazeh nabud ammā sandeviche choritso ālio besyār besyār khoshmazeh bud.</t>
+  </si>
+  <si>
+    <t>Lotf konid az aksoy interneti estefādeh nakonid va akse khode mahsuletuneh bezārin. Ākhe i kojo o u kojo. Mote’asefam.</t>
+  </si>
+  <si>
+    <t>Badjur āsib dideh bud (tebqe akse āplowdshodeh)</t>
+  </si>
+  <si>
+    <t>Joy keyke vanili kākā’ui, keyke kākā’uie sādeh ersal shodeh bud.</t>
+  </si>
+  <si>
+    <t>Khoreshesh mazzey āb midād va navado panj darsade hajme qeymash lappe bud. Aslan pishnāhād namikonam.</t>
+  </si>
+  <si>
+    <t>خورشش مزِّی آب می‌داد و نود و پنج درصد حجم قیمه‌ش لپّه بود. اصلا پیشناهاد نَمی‌کنم.</t>
+  </si>
+  <si>
+    <t>Kheili ālio bemoqeh. Mamnun az shomo.</t>
+  </si>
+  <si>
+    <t>Hajme sāndevichesh kollan nesf shode!</t>
+  </si>
+  <si>
+    <t>Āli. Faghat joy yey changāli khāali bud.</t>
+  </si>
+  <si>
+    <t>عالی. فقط جوی یِی چنگالی خالی بود.</t>
+  </si>
+  <si>
+    <t>Fogholādeh binamak bud va buye tonde gusht midād.</t>
+  </si>
+  <si>
+    <t>Aval ikeh buye bady dosht dovom ikeh beh hame chi mikhord beh joz rost bif juri keh mano yāde gushte ābpaz dākhele ābgusht endākht kheili khis bud nune khoshko badmazei dosht lotfan tanāsobe māye‘āte ra‘āyat konin ehtemālan ākherin bāre ke az injo sefāresh midam.</t>
+  </si>
+  <si>
+    <t>Pas chero namioy?</t>
+  </si>
+  <si>
+    <t>Ma am mioym.</t>
+  </si>
+  <si>
+    <t>Zudi bāsh / Das bojombun</t>
+  </si>
+  <si>
+    <t>زودی باش / دس بجمبون</t>
+  </si>
+  <si>
+    <t>Pas kojoi azizom</t>
+  </si>
+  <si>
+    <t>پس کُجُی عزیزُم؟</t>
+  </si>
+  <si>
+    <t>بیو بیریم ناهار بخوریم. وُی نه، یِی چی آشغالی خوردم، دلُم ریخته به هم.</t>
+  </si>
+  <si>
+    <t>Bio birim nāhār bokhorim. Voy na, yey chi āshghali khordam, delom rikhteh be ham.</t>
+  </si>
+  <si>
+    <t>Mano towo hasan</t>
+  </si>
+  <si>
+    <t>Golo bolbolo sonbol</t>
+  </si>
+  <si>
+    <t>Panjo chāro she</t>
+  </si>
+  <si>
+    <t>Kho pa chro namioy?</t>
+  </si>
+  <si>
+    <t>Kamarom pokid.</t>
+  </si>
+  <si>
+    <t>I kāru ke eqad osom osom kerdan nadāreh keh</t>
+  </si>
+  <si>
+    <t>Ye bār digeh ijuri besheh mikhābam tu kheresh</t>
+  </si>
+  <si>
+    <t>Az beh khub bud kompich gereftam</t>
+  </si>
+  <si>
+    <t>Vasey chi?</t>
+  </si>
+  <si>
+    <t>I khodesho bā shākhe gāv darendākhteh.</t>
+  </si>
+  <si>
+    <t>Khodā dune khadijeh</t>
+  </si>
+  <si>
+    <t>Hālo eqadam beshkano bālo bendāz khub ni</t>
+  </si>
+  <si>
+    <t>Mey dombālet gozoshtan?</t>
+  </si>
+  <si>
+    <r>
+      <t>Nune gandom, kome fulādi mikhā</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>d.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ia nam tok pas namideh</t>
+  </si>
+  <si>
+    <t>چاقوی تیز برِی برِیِ نر اومده.</t>
+  </si>
+  <si>
+    <t>Chāquye tiz barey baareye nar umadeh.</t>
+  </si>
+  <si>
+    <t>Barey khodet bokhor, barey mardom bupush.</t>
+  </si>
+  <si>
+    <t>سُفرِی بابوی شُمو سر کوچه‌ن.</t>
+  </si>
+  <si>
+    <t>Sofrey bāboy shomo sar kuchan.</t>
+  </si>
+  <si>
+    <t>ای شوکوفه‌ها چه قشنگن.</t>
+  </si>
+  <si>
+    <t>I shukufeha che qashangan.</t>
+  </si>
+  <si>
+    <t>Khuney shomo.</t>
+  </si>
+  <si>
+    <t>Khodā khare did behesh shākh nadād</t>
+  </si>
+  <si>
+    <t>Taraf māreh koshteh, bachey māreh zendeh gozoshteh.</t>
+  </si>
+  <si>
+    <t>Jangali shotor dideh.</t>
+  </si>
+  <si>
+    <t>Cheshme zemessun kureh.</t>
+  </si>
+  <si>
+    <t>Gorbow reh borāq kerdeh.</t>
+  </si>
+  <si>
+    <t>فدوی سرت. عیبی نداره.</t>
+  </si>
+  <si>
+    <t>Fadoy saret. Eibi nadāreh.</t>
+  </si>
+  <si>
+    <t>دماغش چقد پَنه. لباش شبی پشت میمونه.</t>
+  </si>
+  <si>
+    <t>Damāghesh cheqad paaneh. Labāsh shabi posthe meymuneh.</t>
+  </si>
+  <si>
+    <t>Engo ureh khānom zoydeh māa reh kaniz.</t>
+  </si>
+  <si>
+    <t>Abdeh i ki bud?</t>
+  </si>
+  <si>
+    <t>Gholām bā abre sia umado dokhtareh beh qasre shāhe pariun bord.</t>
+  </si>
+  <si>
+    <t>I viu cheqad qashangeh.</t>
+  </si>
+  <si>
+    <t>Mikhāma yakhame pāreh konam</t>
+  </si>
+  <si>
+    <t>Gand bokhoreh beh kāret.</t>
+  </si>
+  <si>
+    <t>Barakse mādaresh ke āqel bud khodesh engo diunan.</t>
+  </si>
+  <si>
+    <t>Goshnameh</t>
+  </si>
+  <si>
+    <t>Khers bokhoratesh mipokeh.</t>
+  </si>
+  <si>
+    <t>Harf tā vaqti tu deleteh ekhtiāresh dasseteh.</t>
+  </si>
+  <si>
+    <t>Tor khodā befarmo tu khuneh.</t>
+  </si>
+  <si>
+    <t>تور خدا بفرمو تو خونه.</t>
+  </si>
+  <si>
+    <t>Sākhtane i furudgowam eine raftan be māheh</t>
+  </si>
+  <si>
+    <t>ساختن ای فورودگوَم عین رفتن به ماهه</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -1258,6 +1571,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1399,7 +1718,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1438,6 +1757,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2579,7 +2901,7 @@
     <col min="6" max="6" width="84.5546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="102.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="30" style="1" customWidth="1"/>
+    <col min="9" max="9" width="71.33203125" style="1" customWidth="1"/>
     <col min="10" max="16384" width="8.33203125" style="1"/>
   </cols>
   <sheetData>
@@ -2649,6 +2971,9 @@
       <c r="H3" s="1" t="s">
         <v>249</v>
       </c>
+      <c r="I3" s="1" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="4" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="6" t="s">
@@ -2675,6 +3000,9 @@
       <c r="H4" s="1" t="s">
         <v>250</v>
       </c>
+      <c r="I4" s="1" t="s">
+        <v>429</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="6" t="s">
@@ -2701,6 +3029,12 @@
       <c r="H5" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="I5" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="6" t="s">
@@ -2725,7 +3059,10 @@
         <v>20</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>251</v>
+        <v>314</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1">
@@ -2751,7 +3088,10 @@
         <v>25</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="20.100000000000001" customHeight="1">
@@ -2777,7 +3117,10 @@
         <v>17</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>293</v>
+        <v>280</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="20.100000000000001" customHeight="1">
@@ -2803,7 +3146,10 @@
         <v>17</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="20.100000000000001" customHeight="1">
@@ -2829,7 +3175,10 @@
         <v>14</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1">
@@ -2855,7 +3204,10 @@
         <v>34</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="20.100000000000001" customHeight="1">
@@ -2881,7 +3233,10 @@
         <v>34</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="20.100000000000001" customHeight="1">
@@ -2907,7 +3262,10 @@
         <v>41</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="20.100000000000001" customHeight="1">
@@ -2933,7 +3291,10 @@
         <v>41</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="20.100000000000001" customHeight="1">
@@ -2959,7 +3320,10 @@
         <v>41</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="20.100000000000001" customHeight="1">
@@ -2985,10 +3349,13 @@
         <v>48</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>323</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="6" t="s">
         <v>37</v>
       </c>
@@ -3011,10 +3378,13 @@
         <v>41</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>325</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="6" t="s">
         <v>37</v>
       </c>
@@ -3037,10 +3407,13 @@
         <v>41</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>328</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="6" t="s">
         <v>37</v>
       </c>
@@ -3063,10 +3436,13 @@
         <v>41</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>259</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="6" t="s">
         <v>37</v>
       </c>
@@ -3089,10 +3465,13 @@
         <v>41</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>260</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="6" t="s">
         <v>37</v>
       </c>
@@ -3115,10 +3494,13 @@
         <v>41</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>273</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="6" t="s">
         <v>37</v>
       </c>
@@ -3141,10 +3523,13 @@
         <v>41</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>333</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="6" t="s">
         <v>61</v>
       </c>
@@ -3167,10 +3552,13 @@
         <v>66</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>261</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A24" s="6" t="s">
         <v>61</v>
       </c>
@@ -3193,10 +3581,13 @@
         <v>66</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>262</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A25" s="6" t="s">
         <v>61</v>
       </c>
@@ -3219,10 +3610,13 @@
         <v>71</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>263</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A26" s="6" t="s">
         <v>61</v>
       </c>
@@ -3245,10 +3639,13 @@
         <v>74</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>281</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A27" s="6" t="s">
         <v>61</v>
       </c>
@@ -3271,10 +3668,13 @@
         <v>74</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>282</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="6" t="s">
         <v>61</v>
       </c>
@@ -3297,10 +3697,13 @@
         <v>79</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>274</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="6" t="s">
         <v>61</v>
       </c>
@@ -3323,10 +3726,13 @@
         <v>82</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>264</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -3349,10 +3755,13 @@
         <v>66</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>283</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A31" s="6" t="s">
         <v>61</v>
       </c>
@@ -3375,10 +3784,13 @@
         <v>66</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>284</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="6" t="s">
         <v>61</v>
       </c>
@@ -3403,8 +3815,11 @@
       <c r="H32" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="I32" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A33" s="6" t="s">
         <v>89</v>
       </c>
@@ -3427,10 +3842,13 @@
         <v>94</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>346</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A34" s="6" t="s">
         <v>89</v>
       </c>
@@ -3453,10 +3871,13 @@
         <v>94</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>285</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A35" s="6" t="s">
         <v>89</v>
       </c>
@@ -3479,10 +3900,13 @@
         <v>94</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>286</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A36" s="6" t="s">
         <v>89</v>
       </c>
@@ -3505,10 +3929,13 @@
         <v>94</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>287</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A37" s="6" t="s">
         <v>89</v>
       </c>
@@ -3531,10 +3958,13 @@
         <v>94</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>288</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A38" s="6" t="s">
         <v>89</v>
       </c>
@@ -3557,10 +3987,13 @@
         <v>94</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>289</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A39" s="6" t="s">
         <v>89</v>
       </c>
@@ -3583,10 +4016,13 @@
         <v>94</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>352</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A40" s="6" t="s">
         <v>89</v>
       </c>
@@ -3609,10 +4045,13 @@
         <v>94</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>354</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A41" s="6" t="s">
         <v>89</v>
       </c>
@@ -3635,10 +4074,13 @@
         <v>94</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>290</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A42" s="6" t="s">
         <v>89</v>
       </c>
@@ -3661,10 +4103,16 @@
         <v>94</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="35.549999999999997" customHeight="1">
+        <v>434</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="35.549999999999997" customHeight="1">
       <c r="A43" s="6" t="s">
         <v>113</v>
       </c>
@@ -3687,10 +4135,13 @@
         <v>118</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="35.549999999999997" customHeight="1">
+        <v>291</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="35.549999999999997" customHeight="1">
       <c r="A44" s="6" t="s">
         <v>113</v>
       </c>
@@ -3713,10 +4164,13 @@
         <v>118</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="35.549999999999997" customHeight="1">
+        <v>292</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="35.549999999999997" customHeight="1">
       <c r="A45" s="6" t="s">
         <v>113</v>
       </c>
@@ -3739,10 +4193,13 @@
         <v>118</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="35.549999999999997" customHeight="1">
+        <v>293</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="35.549999999999997" customHeight="1">
       <c r="A46" s="6" t="s">
         <v>113</v>
       </c>
@@ -3765,10 +4222,16 @@
         <v>118</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="35.549999999999997" customHeight="1">
+        <v>294</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="35.549999999999997" customHeight="1">
       <c r="A47" s="6" t="s">
         <v>113</v>
       </c>
@@ -3791,10 +4254,13 @@
         <v>118</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="35.549999999999997" customHeight="1">
+        <v>361</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="35.549999999999997" customHeight="1">
       <c r="A48" s="6" t="s">
         <v>113</v>
       </c>
@@ -3817,10 +4283,13 @@
         <v>118</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="35.549999999999997" customHeight="1">
+        <v>295</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="35.549999999999997" customHeight="1">
       <c r="A49" s="6" t="s">
         <v>113</v>
       </c>
@@ -3843,10 +4312,13 @@
         <v>118</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="35.549999999999997" customHeight="1">
+        <v>296</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="35.549999999999997" customHeight="1">
       <c r="A50" s="6" t="s">
         <v>113</v>
       </c>
@@ -3869,10 +4341,13 @@
         <v>118</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="35.549999999999997" customHeight="1">
+        <v>297</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="35.549999999999997" customHeight="1">
       <c r="A51" s="6" t="s">
         <v>113</v>
       </c>
@@ -3895,10 +4370,13 @@
         <v>118</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="35.549999999999997" customHeight="1">
+        <v>298</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="35.549999999999997" customHeight="1">
       <c r="A52" s="6" t="s">
         <v>113</v>
       </c>
@@ -3921,10 +4399,16 @@
         <v>118</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>368</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A53" s="6" t="s">
         <v>113</v>
       </c>
@@ -3947,10 +4431,13 @@
         <v>139</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>299</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A54" s="6" t="s">
         <v>113</v>
       </c>
@@ -3973,10 +4460,13 @@
         <v>139</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>300</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A55" s="6" t="s">
         <v>113</v>
       </c>
@@ -3999,10 +4489,13 @@
         <v>139</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>265</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A56" s="6" t="s">
         <v>113</v>
       </c>
@@ -4025,10 +4518,13 @@
         <v>139</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>266</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A57" s="6" t="s">
         <v>113</v>
       </c>
@@ -4051,10 +4547,13 @@
         <v>139</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>374</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A58" s="6" t="s">
         <v>113</v>
       </c>
@@ -4077,10 +4576,13 @@
         <v>139</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>267</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A59" s="6" t="s">
         <v>113</v>
       </c>
@@ -4103,10 +4605,13 @@
         <v>139</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>301</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A60" s="6" t="s">
         <v>113</v>
       </c>
@@ -4129,10 +4634,13 @@
         <v>139</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>378</v>
+      </c>
+      <c r="I60" s="13" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A61" s="6" t="s">
         <v>113</v>
       </c>
@@ -4155,10 +4663,13 @@
         <v>139</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A62" s="6" t="s">
         <v>113</v>
       </c>
@@ -4181,10 +4692,13 @@
         <v>139</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>303</v>
+      </c>
+      <c r="I62" s="10" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A63" s="6" t="s">
         <v>113</v>
       </c>
@@ -4207,10 +4721,13 @@
         <v>152</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>268</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A64" s="6" t="s">
         <v>113</v>
       </c>
@@ -4233,10 +4750,13 @@
         <v>152</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>269</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A65" s="6" t="s">
         <v>113</v>
       </c>
@@ -4259,10 +4779,13 @@
         <v>152</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>384</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A66" s="6" t="s">
         <v>113</v>
       </c>
@@ -4285,10 +4808,13 @@
         <v>159</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>386</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A67" s="6" t="s">
         <v>113</v>
       </c>
@@ -4311,10 +4837,13 @@
         <v>159</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>387</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A68" s="6" t="s">
         <v>113</v>
       </c>
@@ -4339,8 +4868,11 @@
       <c r="H68" s="1" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="I68" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A69" s="6" t="s">
         <v>113</v>
       </c>
@@ -4365,8 +4897,11 @@
       <c r="H69" s="1" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="I69" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A70" s="6" t="s">
         <v>113</v>
       </c>
@@ -4389,10 +4924,13 @@
         <v>152</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>270</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A71" s="6" t="s">
         <v>113</v>
       </c>
@@ -4415,10 +4953,13 @@
         <v>152</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>304</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A72" s="6" t="s">
         <v>113</v>
       </c>
@@ -4441,10 +4982,13 @@
         <v>159</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>271</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A73" s="6" t="s">
         <v>113</v>
       </c>
@@ -4469,8 +5013,11 @@
       <c r="H73" s="1" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="I73" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A74" s="6" t="s">
         <v>113</v>
       </c>
@@ -4495,8 +5042,11 @@
       <c r="H74" s="1" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="I74" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A75" s="6" t="s">
         <v>113</v>
       </c>
@@ -4521,8 +5071,11 @@
       <c r="H75" s="1" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="I75" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A76" s="6" t="s">
         <v>113</v>
       </c>
@@ -4547,8 +5100,11 @@
       <c r="H76" s="1" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="I76" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A77" s="6" t="s">
         <v>113</v>
       </c>
@@ -4573,8 +5129,11 @@
       <c r="H77" s="1" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="I77" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A78" s="6" t="s">
         <v>113</v>
       </c>
@@ -4599,8 +5158,11 @@
       <c r="H78" s="1" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="I78" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A79" s="6" t="s">
         <v>113</v>
       </c>
@@ -4625,8 +5187,11 @@
       <c r="H79" s="1" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="I79" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A80" s="6" t="s">
         <v>113</v>
       </c>
@@ -4651,8 +5216,11 @@
       <c r="H80" s="1" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="I80" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A81" s="6" t="s">
         <v>113</v>
       </c>
@@ -4677,8 +5245,11 @@
       <c r="H81" s="1" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="I81" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A82" s="6" t="s">
         <v>113</v>
       </c>
@@ -4703,8 +5274,11 @@
       <c r="H82" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="I82" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A83" s="6" t="s">
         <v>196</v>
       </c>
@@ -4727,10 +5301,13 @@
         <v>199</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>404</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A84" s="6" t="s">
         <v>196</v>
       </c>
@@ -4753,10 +5330,13 @@
         <v>199</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>305</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A85" s="6" t="s">
         <v>196</v>
       </c>
@@ -4779,10 +5359,13 @@
         <v>204</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>407</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A86" s="6" t="s">
         <v>196</v>
       </c>
@@ -4805,10 +5388,13 @@
         <v>207</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>409</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A87" s="6" t="s">
         <v>196</v>
       </c>
@@ -4831,10 +5417,13 @@
         <v>207</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>272</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A88" s="6" t="s">
         <v>196</v>
       </c>
@@ -4857,10 +5446,13 @@
         <v>212</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>306</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A89" s="6" t="s">
         <v>196</v>
       </c>
@@ -4883,10 +5475,16 @@
         <v>204</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>307</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A90" s="6" t="s">
         <v>196</v>
       </c>
@@ -4911,8 +5509,11 @@
       <c r="H90" s="1" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="I90" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A91" s="6" t="s">
         <v>196</v>
       </c>
@@ -4935,10 +5536,16 @@
         <v>199</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>309</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A92" s="6" t="s">
         <v>196</v>
       </c>
@@ -4961,10 +5568,16 @@
         <v>199</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>279</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A93" s="6" t="s">
         <v>221</v>
       </c>
@@ -4987,10 +5600,13 @@
         <v>41</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>417</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A94" s="6" t="s">
         <v>221</v>
       </c>
@@ -5013,10 +5629,16 @@
         <v>41</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>419</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A95" s="6" t="s">
         <v>221</v>
       </c>
@@ -5039,10 +5661,13 @@
         <v>41</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>310</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A96" s="6" t="s">
         <v>221</v>
       </c>
@@ -5065,10 +5690,16 @@
         <v>41</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>432</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A97" s="6" t="s">
         <v>221</v>
       </c>
@@ -5091,10 +5722,16 @@
         <v>233</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>278</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A98" s="6" t="s">
         <v>221</v>
       </c>
@@ -5117,10 +5754,13 @@
         <v>236</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>277</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A99" s="6" t="s">
         <v>221</v>
       </c>
@@ -5143,10 +5783,13 @@
         <v>239</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>276</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A100" s="6" t="s">
         <v>221</v>
       </c>
@@ -5169,10 +5812,13 @@
         <v>242</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>311</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A101" s="6" t="s">
         <v>221</v>
       </c>
@@ -5195,10 +5841,13 @@
         <v>41</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" ht="20.100000000000001" customHeight="1">
+        <v>308</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A102" s="6" t="s">
         <v>221</v>
       </c>
@@ -5221,7 +5870,10 @@
         <v>41</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>286</v>
+        <v>275</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -5279,7 +5931,7 @@
     <hyperlink ref="G100" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId49"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/datasets/100_samples_shirazi.xlsx
+++ b/datasets/100_samples_shirazi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Personal Projects\SilkRoadNLP\Repositories\General\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADD8B71-80E9-483E-BACC-E5F73E4ACA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC55C64-C143-43D9-B2D8-0265DB653577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="436">
   <si>
     <t>100_samples</t>
   </si>
@@ -1095,9 +1095,6 @@
     <t>ما برِی تازه‌ترین آتیش منتظر می‌مونیم</t>
   </si>
   <si>
-    <t>مِثکه کسوی دیگه‌ای هم با هواپیما به لوگر می‌رن</t>
-  </si>
-  <si>
     <t>درخت میوه کرم از خودشه</t>
   </si>
   <si>
@@ -1188,9 +1185,6 @@
     <t>Dokhtarā doshtan miraftan</t>
   </si>
   <si>
-    <t>Ravānshenāsā khavāse ziādi barey gerye kerdan dar ovordan va gerye kerdane barey rahā shodan az feshāre esteres va tahammole dardo ghamo ghose midunan.</t>
-  </si>
-  <si>
     <t>U morabow khordan dāreh</t>
   </si>
   <si>
@@ -1218,9 +1212,6 @@
     <t>Ey junom barey shahremun</t>
   </si>
   <si>
-    <t>Dorude farāvun be zanoy korde sar tā sare donyā az kermunshā gerefte ta kordestān</t>
-  </si>
-  <si>
     <t>Har vaght nun doros mikerd sedāmun mizad. Mā bachchā ham hamegi be saf kenāresh mishnessimo cheshm be rā mimondim tā nun ruye towe bereshte mishodo midād dassemun.</t>
   </si>
   <si>
@@ -1284,36 +1275,21 @@
     <t>یَنی ساخته نمی‌شه</t>
   </si>
   <si>
-    <t>Yani sakhteh namisheh</t>
-  </si>
-  <si>
     <t>با ایکه دَ تو کارگر داره،‌ پونزَ سال طول می‌کشه</t>
   </si>
   <si>
     <t>Bā ike da to kārgar dāreh, punza sāl tul mikeshe</t>
   </si>
   <si>
-    <t>Meske kasoy degei ham bā hāvāpeyma be logar miran</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
     <t>Derakhte mive kerm az khodeshe</t>
   </si>
   <si>
     <t>Birune bāgho ke didim, engo tā tahe bāgho didim.</t>
   </si>
   <si>
-    <t>Hareh ay dākhele shisheh koni beh birun darz mikoneh.</t>
-  </si>
-  <si>
     <t>دل که سفره نیس که پیش همه پهنش کنی.</t>
   </si>
   <si>
-    <t>Del ke sofre nis ke pishe hame pahnesh koni.</t>
-  </si>
-  <si>
     <t>Kherso be āhangari bassan.</t>
   </si>
   <si>
@@ -1326,18 +1302,9 @@
     <t>Āyat kāret akhere.</t>
   </si>
   <si>
-    <t>Chākan hamisheh ta chāheh.</t>
-  </si>
-  <si>
     <t>چاکَن همیشه تَ چاهه.</t>
   </si>
   <si>
-    <t>Qeymate ghazā nesbat beh hajme ghazā kheili geruno gheyremonsefānan. Sāndeviche hayuloy zhāmbon dar hadde yey bachche ghuli ham nabud va aslan ham khoshmazeh nabud ammā sandeviche choritso ālio besyār besyār khoshmazeh bud.</t>
-  </si>
-  <si>
-    <t>Lotf konid az aksoy interneti estefādeh nakonid va akse khode mahsuletuneh bezārin. Ākhe i kojo o u kojo. Mote’asefam.</t>
-  </si>
-  <si>
     <t>Badjur āsib dideh bud (tebqe akse āplowdshodeh)</t>
   </si>
   <si>
@@ -1350,12 +1317,6 @@
     <t>خورشش مزِّی آب می‌داد و نود و پنج درصد حجم قیمه‌ش لپّه بود. اصلا پیشناهاد نَمی‌کنم.</t>
   </si>
   <si>
-    <t>Kheili ālio bemoqeh. Mamnun az shomo.</t>
-  </si>
-  <si>
-    <t>Hajme sāndevichesh kollan nesf shode!</t>
-  </si>
-  <si>
     <t>Āli. Faghat joy yey changāli khāali bud.</t>
   </si>
   <si>
@@ -1365,12 +1326,6 @@
     <t>Fogholādeh binamak bud va buye tonde gusht midād.</t>
   </si>
   <si>
-    <t>Aval ikeh buye bady dosht dovom ikeh beh hame chi mikhord beh joz rost bif juri keh mano yāde gushte ābpaz dākhele ābgusht endākht kheili khis bud nune khoshko badmazei dosht lotfan tanāsobe māye‘āte ra‘āyat konin ehtemālan ākherin bāre ke az injo sefāresh midam.</t>
-  </si>
-  <si>
-    <t>Pas chero namioy?</t>
-  </si>
-  <si>
     <t>Ma am mioym.</t>
   </si>
   <si>
@@ -1380,43 +1335,22 @@
     <t>زودی باش / دس بجمبون</t>
   </si>
   <si>
-    <t>Pas kojoi azizom</t>
-  </si>
-  <si>
     <t>پس کُجُی عزیزُم؟</t>
   </si>
   <si>
     <t>بیو بیریم ناهار بخوریم. وُی نه، یِی چی آشغالی خوردم، دلُم ریخته به هم.</t>
   </si>
   <si>
-    <t>Bio birim nāhār bokhorim. Voy na, yey chi āshghali khordam, delom rikhteh be ham.</t>
-  </si>
-  <si>
     <t>Mano towo hasan</t>
   </si>
   <si>
-    <t>Golo bolbolo sonbol</t>
-  </si>
-  <si>
-    <t>Panjo chāro she</t>
-  </si>
-  <si>
-    <t>Kho pa chro namioy?</t>
-  </si>
-  <si>
     <t>Kamarom pokid.</t>
   </si>
   <si>
     <t>I kāru ke eqad osom osom kerdan nadāreh keh</t>
   </si>
   <si>
-    <t>Ye bār digeh ijuri besheh mikhābam tu kheresh</t>
-  </si>
-  <si>
     <t>Az beh khub bud kompich gereftam</t>
-  </si>
-  <si>
-    <t>Vasey chi?</t>
   </si>
   <si>
     <t>I khodesho bā shākhe gāv darendākhteh.</t>
@@ -1444,9 +1378,6 @@
     </r>
   </si>
   <si>
-    <t>Ia nam tok pas namideh</t>
-  </si>
-  <si>
     <t>چاقوی تیز برِی برِیِ نر اومده.</t>
   </si>
   <si>
@@ -1474,70 +1405,142 @@
     <t>Khodā khare did behesh shākh nadād</t>
   </si>
   <si>
-    <t>Taraf māreh koshteh, bachey māreh zendeh gozoshteh.</t>
-  </si>
-  <si>
     <t>Jangali shotor dideh.</t>
   </si>
   <si>
-    <t>Cheshme zemessun kureh.</t>
-  </si>
-  <si>
-    <t>Gorbow reh borāq kerdeh.</t>
-  </si>
-  <si>
     <t>فدوی سرت. عیبی نداره.</t>
   </si>
   <si>
-    <t>Fadoy saret. Eibi nadāreh.</t>
-  </si>
-  <si>
     <t>دماغش چقد پَنه. لباش شبی پشت میمونه.</t>
   </si>
   <si>
-    <t>Damāghesh cheqad paaneh. Labāsh shabi posthe meymuneh.</t>
-  </si>
-  <si>
-    <t>Engo ureh khānom zoydeh māa reh kaniz.</t>
-  </si>
-  <si>
     <t>Abdeh i ki bud?</t>
   </si>
   <si>
-    <t>Gholām bā abre sia umado dokhtareh beh qasre shāhe pariun bord.</t>
-  </si>
-  <si>
-    <t>I viu cheqad qashangeh.</t>
-  </si>
-  <si>
-    <t>Mikhāma yakhame pāreh konam</t>
-  </si>
-  <si>
-    <t>Gand bokhoreh beh kāret.</t>
-  </si>
-  <si>
     <t>Barakse mādaresh ke āqel bud khodesh engo diunan.</t>
   </si>
   <si>
-    <t>Goshnameh</t>
-  </si>
-  <si>
     <t>Khers bokhoratesh mipokeh.</t>
   </si>
   <si>
-    <t>Harf tā vaqti tu deleteh ekhtiāresh dasseteh.</t>
-  </si>
-  <si>
     <t>Tor khodā befarmo tu khuneh.</t>
   </si>
   <si>
     <t>تور خدا بفرمو تو خونه.</t>
   </si>
   <si>
-    <t>Sākhtane i furudgowam eine raftan be māheh</t>
-  </si>
-  <si>
     <t>ساختن ای فورودگوَم عین رفتن به ماهه</t>
+  </si>
+  <si>
+    <t>Goshname</t>
+  </si>
+  <si>
+    <t>Ravānshenāsā khavāse ziādi barey geryeh kerdan dar ovordan va geryeh kerdane barey rahā shodan az feshāre esteres va tahammole dardo ghamo ghose midunan.</t>
+  </si>
+  <si>
+    <t>Dorude farāvun be zanoy korde sar tā sare donyā az kermunshā gerefteh ta kordestān</t>
+  </si>
+  <si>
+    <t>Yani sākhteh namisheh</t>
+  </si>
+  <si>
+    <t>مِثکه کسوی دیگِیِم با هواپیما به لوگر می‌رن</t>
+  </si>
+  <si>
+    <t>Meske kasoy degeiam bā hāvāpeyma be logar miran</t>
+  </si>
+  <si>
+    <t>Sākhtane i furudgowam eine raftan be māhe</t>
+  </si>
+  <si>
+    <t>Harfe ay dākhele shisheh koni be birun darz mikoneh.</t>
+  </si>
+  <si>
+    <t>Harf tā vaqti tu delete ekhtiāresh dassete.</t>
+  </si>
+  <si>
+    <t>Del ke sofreh nis ke pishe hameh pahnesh koni.</t>
+  </si>
+  <si>
+    <t>Chākan hamisheh ta chāhe.</t>
+  </si>
+  <si>
+    <t>Qeymate ghazā nesbat be hajme ghazā kheili geruno gheyremonsefānan. Sāndeviche hayuloy zhāmbon dar hadde yey bachcheh ghuli ham nabud va aslan ham khoshmazeh nabud ammā sandeviche choritso ālio besyār besyār khoshmazeh bud.</t>
+  </si>
+  <si>
+    <t>Lotf konid az aksoy interneti estefādeh nakonid va akse khode mahsuletune bezārin. Ākhe i kojo o u kojo. Mote’asefam.</t>
+  </si>
+  <si>
+    <t>Kheili ālio bemoqe‘. Mamnun az shomo.</t>
+  </si>
+  <si>
+    <t>Hajme sāndevichesh kollan nesf shodeh!</t>
+  </si>
+  <si>
+    <t>Aval ike buye badi dosht dovom ike be hame chi mikhord be joz rost bif juri ke mano yāde gushte ābpaz dākhele ābgusht endākht kheili khis bud nune khoshko badmazei dosht lotfan tanāsobe māye‘āte ra‘āyat konin ehtemālan ākherin bāre ke az injo sefāresh midam.</t>
+  </si>
+  <si>
+    <t>Pas chero namyoy?</t>
+  </si>
+  <si>
+    <t>Pas kojoy azizom</t>
+  </si>
+  <si>
+    <t>Bio birim nāhār bokhorim. Voy na, yey chi āshghāli khordam, delom rikhteh be ham.</t>
+  </si>
+  <si>
+    <t>گل و بلبل و سمبل</t>
+  </si>
+  <si>
+    <t>Golo bolbolo sombol</t>
+  </si>
+  <si>
+    <t>Panjo chāro seh</t>
+  </si>
+  <si>
+    <t>Kho pa chero namioy?</t>
+  </si>
+  <si>
+    <t>ای کارو که اقد اُسُم اُسُم کردن نداره که</t>
+  </si>
+  <si>
+    <t>Ye bār dige ijuri besheh mikhābam tu kheresh</t>
+  </si>
+  <si>
+    <t>Vāsey chi?</t>
+  </si>
+  <si>
+    <t>Iyā nam tok pas namideh</t>
+  </si>
+  <si>
+    <t>Taraf māre koshteh, bachey māre zendeh gozoshteh.</t>
+  </si>
+  <si>
+    <t>Cheshme zemessun kure.</t>
+  </si>
+  <si>
+    <t>Gorbow re borāq kerdeh.</t>
+  </si>
+  <si>
+    <t>Fadoy saret. Eybi nadāreh.</t>
+  </si>
+  <si>
+    <t>Damāghesh cheqad paane. Labāsh shabi poshte meymune.</t>
+  </si>
+  <si>
+    <t>Engo ure khānom zoydeh māa re kaniz.</t>
+  </si>
+  <si>
+    <t>Gholām bā abre siā umado dokhtare be qasre shāhe pariun bord.</t>
+  </si>
+  <si>
+    <t>I viu cheqad qashange.</t>
+  </si>
+  <si>
+    <t>Mikhāmā yakhame pāreh konam</t>
+  </si>
+  <si>
+    <t>Gand bokhoreh be kāret.</t>
   </si>
 </sst>
 </file>
@@ -1718,7 +1721,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1752,14 +1755,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2891,7 +2891,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr defaultColWidth="8.33203125" defaultRowHeight="19.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1" customWidth="1"/>
@@ -2905,7 +2905,7 @@
     <col min="10" max="16384" width="8.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27.6" customHeight="1">
+    <row r="1" spans="1:9" ht="27.6" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -2916,7 +2916,7 @@
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
     </row>
-    <row r="2" spans="1:10" ht="20.25" customHeight="1">
+    <row r="2" spans="1:9" ht="20.25" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2944,9 +2944,8 @@
       <c r="I2" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="3" spans="1:10" ht="20.25" customHeight="1">
+    </row>
+    <row r="3" spans="1:9" ht="20.25" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -2972,10 +2971,10 @@
         <v>249</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
@@ -3001,10 +3000,10 @@
         <v>250</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
@@ -3030,13 +3029,10 @@
         <v>19</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
@@ -3059,13 +3055,13 @@
         <v>20</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>8</v>
       </c>
@@ -3091,10 +3087,10 @@
         <v>251</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
@@ -3116,14 +3112,14 @@
       <c r="G8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="1" t="s">
         <v>280</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
@@ -3149,10 +3145,10 @@
         <v>252</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
@@ -3178,10 +3174,10 @@
         <v>253</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="6" t="s">
         <v>8</v>
       </c>
@@ -3207,10 +3203,10 @@
         <v>254</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="6" t="s">
         <v>8</v>
       </c>
@@ -3236,10 +3232,10 @@
         <v>255</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="6" t="s">
         <v>37</v>
       </c>
@@ -3265,10 +3261,10 @@
         <v>256</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="6" t="s">
         <v>37</v>
       </c>
@@ -3294,10 +3290,10 @@
         <v>257</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="6" t="s">
         <v>37</v>
       </c>
@@ -3323,10 +3319,10 @@
         <v>258</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="6" t="s">
         <v>37</v>
       </c>
@@ -3349,10 +3345,10 @@
         <v>48</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -3378,10 +3374,10 @@
         <v>41</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -3407,10 +3403,10 @@
         <v>41</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -3439,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -3468,7 +3464,7 @@
         <v>260</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -3497,7 +3493,7 @@
         <v>273</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -3523,10 +3519,10 @@
         <v>41</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -3555,7 +3551,7 @@
         <v>261</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -3584,7 +3580,7 @@
         <v>262</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -3613,7 +3609,7 @@
         <v>263</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -3642,7 +3638,7 @@
         <v>281</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -3671,7 +3667,7 @@
         <v>282</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -3700,7 +3696,7 @@
         <v>274</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -3729,7 +3725,7 @@
         <v>264</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -3758,7 +3754,7 @@
         <v>283</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -3787,7 +3783,7 @@
         <v>284</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -3816,10 +3812,10 @@
         <v>88</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A33" s="6" t="s">
         <v>89</v>
       </c>
@@ -3842,13 +3838,13 @@
         <v>94</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A34" s="6" t="s">
         <v>89</v>
       </c>
@@ -3874,10 +3870,10 @@
         <v>285</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A35" s="6" t="s">
         <v>89</v>
       </c>
@@ -3903,10 +3899,10 @@
         <v>286</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A36" s="6" t="s">
         <v>89</v>
       </c>
@@ -3932,10 +3928,10 @@
         <v>287</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A37" s="6" t="s">
         <v>89</v>
       </c>
@@ -3961,10 +3957,10 @@
         <v>288</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A38" s="6" t="s">
         <v>89</v>
       </c>
@@ -3990,10 +3986,10 @@
         <v>289</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A39" s="6" t="s">
         <v>89</v>
       </c>
@@ -4016,13 +4012,13 @@
         <v>94</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A40" s="6" t="s">
         <v>89</v>
       </c>
@@ -4045,13 +4041,13 @@
         <v>94</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A41" s="6" t="s">
         <v>89</v>
       </c>
@@ -4074,13 +4070,13 @@
         <v>94</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>290</v>
+        <v>403</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A42" s="6" t="s">
         <v>89</v>
       </c>
@@ -4103,16 +4099,13 @@
         <v>94</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>434</v>
+        <v>398</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="35.549999999999997" customHeight="1">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="35.549999999999997" customHeight="1">
       <c r="A43" s="6" t="s">
         <v>113</v>
       </c>
@@ -4135,13 +4128,13 @@
         <v>118</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="35.549999999999997" customHeight="1">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="35.549999999999997" customHeight="1">
       <c r="A44" s="6" t="s">
         <v>113</v>
       </c>
@@ -4164,13 +4157,13 @@
         <v>118</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="35.549999999999997" customHeight="1">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="35.549999999999997" customHeight="1">
       <c r="A45" s="6" t="s">
         <v>113</v>
       </c>
@@ -4193,13 +4186,13 @@
         <v>118</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="35.549999999999997" customHeight="1">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="35.549999999999997" customHeight="1">
       <c r="A46" s="6" t="s">
         <v>113</v>
       </c>
@@ -4222,16 +4215,13 @@
         <v>118</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="35.549999999999997" customHeight="1">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="35.549999999999997" customHeight="1">
       <c r="A47" s="6" t="s">
         <v>113</v>
       </c>
@@ -4254,13 +4244,13 @@
         <v>118</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="35.549999999999997" customHeight="1">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="35.549999999999997" customHeight="1">
       <c r="A48" s="6" t="s">
         <v>113</v>
       </c>
@@ -4283,13 +4273,13 @@
         <v>118</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="35.549999999999997" customHeight="1">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="35.549999999999997" customHeight="1">
       <c r="A49" s="6" t="s">
         <v>113</v>
       </c>
@@ -4312,13 +4302,13 @@
         <v>118</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="35.549999999999997" customHeight="1">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="35.549999999999997" customHeight="1">
       <c r="A50" s="6" t="s">
         <v>113</v>
       </c>
@@ -4341,13 +4331,13 @@
         <v>118</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="35.549999999999997" customHeight="1">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="35.549999999999997" customHeight="1">
       <c r="A51" s="6" t="s">
         <v>113</v>
       </c>
@@ -4370,13 +4360,13 @@
         <v>118</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="35.549999999999997" customHeight="1">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="35.549999999999997" customHeight="1">
       <c r="A52" s="6" t="s">
         <v>113</v>
       </c>
@@ -4399,16 +4389,13 @@
         <v>118</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A53" s="6" t="s">
         <v>113</v>
       </c>
@@ -4431,13 +4418,13 @@
         <v>139</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A54" s="6" t="s">
         <v>113</v>
       </c>
@@ -4460,13 +4447,13 @@
         <v>139</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A55" s="6" t="s">
         <v>113</v>
       </c>
@@ -4492,10 +4479,10 @@
         <v>265</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A56" s="6" t="s">
         <v>113</v>
       </c>
@@ -4521,10 +4508,10 @@
         <v>266</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A57" s="6" t="s">
         <v>113</v>
       </c>
@@ -4547,13 +4534,13 @@
         <v>139</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A58" s="6" t="s">
         <v>113</v>
       </c>
@@ -4579,10 +4566,10 @@
         <v>267</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A59" s="6" t="s">
         <v>113</v>
       </c>
@@ -4605,13 +4592,13 @@
         <v>139</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A60" s="6" t="s">
         <v>113</v>
       </c>
@@ -4634,13 +4621,13 @@
         <v>139</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="I60" s="13" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>365</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A61" s="6" t="s">
         <v>113</v>
       </c>
@@ -4663,13 +4650,13 @@
         <v>139</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A62" s="6" t="s">
         <v>113</v>
       </c>
@@ -4692,13 +4679,13 @@
         <v>139</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A63" s="6" t="s">
         <v>113</v>
       </c>
@@ -4724,10 +4711,10 @@
         <v>268</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A64" s="6" t="s">
         <v>113</v>
       </c>
@@ -4753,7 +4740,7 @@
         <v>269</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -4779,10 +4766,10 @@
         <v>152</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -4808,10 +4795,10 @@
         <v>159</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>385</v>
+        <v>416</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -4837,10 +4824,10 @@
         <v>159</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -4869,7 +4856,7 @@
         <v>163</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -4895,10 +4882,10 @@
         <v>152</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>165</v>
+        <v>418</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>390</v>
+        <v>419</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -4927,7 +4914,7 @@
         <v>270</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -4953,10 +4940,10 @@
         <v>152</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -4985,7 +4972,7 @@
         <v>271</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -5011,10 +4998,10 @@
         <v>41</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>173</v>
+        <v>422</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -5043,7 +5030,7 @@
         <v>175</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -5072,7 +5059,7 @@
         <v>177</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>396</v>
+        <v>375</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -5101,7 +5088,7 @@
         <v>179</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -5130,7 +5117,7 @@
         <v>182</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>398</v>
+        <v>376</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -5159,7 +5146,7 @@
         <v>185</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -5188,7 +5175,7 @@
         <v>188</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>400</v>
+        <v>378</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -5217,10 +5204,10 @@
         <v>190</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A81" s="6" t="s">
         <v>113</v>
       </c>
@@ -5246,10 +5233,10 @@
         <v>192</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A82" s="6" t="s">
         <v>113</v>
       </c>
@@ -5275,10 +5262,10 @@
         <v>194</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A83" s="6" t="s">
         <v>196</v>
       </c>
@@ -5301,13 +5288,13 @@
         <v>199</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>404</v>
+        <v>381</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A84" s="6" t="s">
         <v>196</v>
       </c>
@@ -5330,13 +5317,13 @@
         <v>199</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A85" s="6" t="s">
         <v>196</v>
       </c>
@@ -5359,13 +5346,13 @@
         <v>204</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>407</v>
+        <v>384</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A86" s="6" t="s">
         <v>196</v>
       </c>
@@ -5388,13 +5375,13 @@
         <v>207</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>409</v>
+        <v>386</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A87" s="6" t="s">
         <v>196</v>
       </c>
@@ -5420,10 +5407,10 @@
         <v>272</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A88" s="6" t="s">
         <v>196</v>
       </c>
@@ -5446,13 +5433,13 @@
         <v>212</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A89" s="6" t="s">
         <v>196</v>
       </c>
@@ -5475,16 +5462,13 @@
         <v>204</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="J89" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A90" s="6" t="s">
         <v>196</v>
       </c>
@@ -5510,10 +5494,10 @@
         <v>216</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A91" s="6" t="s">
         <v>196</v>
       </c>
@@ -5536,16 +5520,13 @@
         <v>199</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A92" s="6" t="s">
         <v>196</v>
       </c>
@@ -5571,13 +5552,10 @@
         <v>279</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A93" s="6" t="s">
         <v>221</v>
       </c>
@@ -5600,13 +5578,13 @@
         <v>41</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A94" s="6" t="s">
         <v>221</v>
       </c>
@@ -5629,16 +5607,13 @@
         <v>41</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A95" s="6" t="s">
         <v>221</v>
       </c>
@@ -5660,14 +5635,14 @@
       <c r="G95" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H95" s="11" t="s">
-        <v>310</v>
+      <c r="H95" s="1" t="s">
+        <v>309</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A96" s="6" t="s">
         <v>221</v>
       </c>
@@ -5690,16 +5665,13 @@
         <v>41</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>432</v>
+        <v>397</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="J96" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A97" s="6" t="s">
         <v>221</v>
       </c>
@@ -5725,13 +5697,10 @@
         <v>278</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="J97" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A98" s="6" t="s">
         <v>221</v>
       </c>
@@ -5757,10 +5726,10 @@
         <v>277</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A99" s="6" t="s">
         <v>221</v>
       </c>
@@ -5786,10 +5755,10 @@
         <v>276</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A100" s="6" t="s">
         <v>221</v>
       </c>
@@ -5812,13 +5781,13 @@
         <v>242</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A101" s="6" t="s">
         <v>221</v>
       </c>
@@ -5841,13 +5810,13 @@
         <v>41</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" ht="20.100000000000001" customHeight="1">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A102" s="6" t="s">
         <v>221</v>
       </c>
@@ -5873,7 +5842,7 @@
         <v>275</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>427</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
